--- a/04_DESIGN_TABLES/DesignTable_5501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,6 +1786,332 @@
       <c r="AU8" t="inlineStr">
         <is>
           <t>5501-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.08203</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>5501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>45 deg Male Pipe Elbow, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | 2026-10-20 (batch 19 D_geom): N4 / N6 / flats / bores from OMi WebsitePartsInfo2026.xlsx (07_RAW_EXTRACTS/omi_dimensions, sha256 e5109342e141...) Items row 1456 (= Brennan TFA catalog p.31 5501-24-24-FG on all 5 values, one source) - ASSUMED; NPTF majors from the end library; the angled-leg helix thread (gate Q-NEW-ANGLEDHELIX) is in the generators since batch 17 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF end on the 45 deg leg (Q-NEW-ANGLEDHELIX): the library male end of the axis legs (ASME B1.20.3 cone + relief to the 5404 end length) turned to the 135 deg axis; its bore ends at the axis crossing as on every built root (Brennan 5501-08-08-FG / 5503-16-16-FG STEPs, OCP 2026-10-18: the male drill runs on a little past the crossing, and Brennan draws its own simplified thread cone and a bore-mouth countersink - NOT modelled); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20: filled from OMi's file row 1456 (= Brennan TFA p.31), ASSUMED; Air-Way prints no 5501-24-24 -FG row (its non-FG 5501-24-24 is not used) | leg 1: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>5501-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.44288</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>5501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>45 deg Male Pipe Elbow, 2-11 1/2 NPTF x 2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | 2026-10-20 (batch 19 D_geom): N4 / N6 / flats / bores from OMi WebsitePartsInfo2026.xlsx (07_RAW_EXTRACTS/omi_dimensions, sha256 e5109342e141...) Items row 1457 (Brennan's catalog table ends at -24: OMi's file is the only source) - ASSUMED; NPTF majors from the end library; the angled-leg helix thread is in the generators since batch 17 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF end on the 45 deg leg (Q-NEW-ANGLEDHELIX): the library male end of the axis legs (ASME B1.20.3 cone + relief to the 5404 end length) turned to the 135 deg axis; its bore ends at the axis crossing as on every built root (Brennan 5501-08-08-FG / 5503-16-16-FG STEPs, OCP 2026-10-18: the male drill runs on a little past the crossing, and Brennan draws its own simplified thread cone and a bore-mouth countersink - NOT modelled); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20: filled from OMi's file row 1457, ASSUMED (single source); Air-Way prints no 5501-32-32 row</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>5501-32-32-FG</t>
         </is>
       </c>
     </row>
